--- a/Mapas/Excels/REE.xlsx
+++ b/Mapas/Excels/REE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseantonio.alvarez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3A6503-A411-43E2-A2BC-1F879CD104CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F3430E-26CF-46A2-B50C-5162B1BCCE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5282,9 +5282,6 @@
     <t>TARIFA</t>
   </si>
   <si>
-    <t xml:space="preserve">36.03232750278472, </t>
-  </si>
-  <si>
     <t>-5.605888261046909</t>
   </si>
   <si>
@@ -5337,6 +5334,9 @@
   </si>
   <si>
     <t>28.132759917234797</t>
+  </si>
+  <si>
+    <t>36.03232750278472</t>
   </si>
 </sst>
 </file>
@@ -12022,10 +12022,10 @@
         <v>13</v>
       </c>
       <c r="E271" s="5" t="s">
+        <v>1749</v>
+      </c>
+      <c r="F271" s="5" t="s">
         <v>1750</v>
-      </c>
-      <c r="F271" s="5" t="s">
-        <v>1751</v>
       </c>
       <c r="G271" s="3" t="s">
         <v>1098</v>
@@ -13250,7 +13250,7 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="B324" t="s">
         <v>23</v>
@@ -13262,10 +13262,10 @@
         <v>66</v>
       </c>
       <c r="E324" s="5" t="s">
+        <v>1764</v>
+      </c>
+      <c r="F324" s="5" t="s">
         <v>1765</v>
-      </c>
-      <c r="F324" s="5" t="s">
-        <v>1766</v>
       </c>
       <c r="G324" s="3" t="s">
         <v>1498</v>
@@ -20574,7 +20574,7 @@
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="B636" t="s">
         <v>20</v>
@@ -20586,10 +20586,10 @@
         <v>220</v>
       </c>
       <c r="E636" s="3" t="s">
+        <v>1752</v>
+      </c>
+      <c r="F636" s="5" t="s">
         <v>1753</v>
-      </c>
-      <c r="F636" s="5" t="s">
-        <v>1754</v>
       </c>
       <c r="H636" s="3"/>
     </row>
@@ -21271,7 +21271,7 @@
     </row>
     <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="B666" t="s">
         <v>27</v>
@@ -21283,10 +21283,10 @@
         <v>220</v>
       </c>
       <c r="E666" s="5" t="s">
+        <v>1755</v>
+      </c>
+      <c r="F666" s="5" t="s">
         <v>1756</v>
-      </c>
-      <c r="F666" s="5" t="s">
-        <v>1757</v>
       </c>
       <c r="G666" t="s">
         <v>991</v>
@@ -22169,7 +22169,7 @@
     </row>
     <row r="704" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="B704" t="s">
         <v>20</v>
@@ -22184,10 +22184,10 @@
         <v>-7.1887699999999999</v>
       </c>
       <c r="F704" s="5" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="G704" s="3" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H704" s="3"/>
     </row>
@@ -22555,10 +22555,10 @@
         <v>400</v>
       </c>
       <c r="E720" s="3" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="F720" s="5" t="s">
-        <v>1748</v>
+        <v>1766</v>
       </c>
       <c r="G720" s="3" t="s">
         <v>970</v>
@@ -23507,7 +23507,7 @@
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="B761" t="s">
         <v>27</v>
@@ -23519,10 +23519,10 @@
         <v>220</v>
       </c>
       <c r="E761" s="5" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F761" s="5" t="s">
         <v>1762</v>
-      </c>
-      <c r="F761" s="5" t="s">
-        <v>1763</v>
       </c>
       <c r="G761" s="3" t="s">
         <v>1498</v>
